--- a/LinktoExperiments.xlsx
+++ b/LinktoExperiments.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mt1102\Documents\Python Scripts\CellTrackScatterPlots\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FCAADAF-EB2E-469E-AF87-88D4D5E6F51D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{637D0C5A-1E93-448A-B05F-5DB6F3D7B648}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,36 +25,24 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
     <t>experiment_path</t>
   </si>
   <si>
-    <t>C:\Users\mt1102\Box\Nabeel Tahir Meetings\Meetings\Weekly Meetings\Meeting Jan 2026\Experiment 1_14_2026\Sample 1</t>
-  </si>
-  <si>
-    <t>C:\Users\mt1102\Box\Nabeel Tahir Meetings\Meetings\Weekly Meetings\Meeting Jan 2026\Experiment 1_14_2026\Sample 2</t>
-  </si>
-  <si>
-    <t>C:\Users\mt1102\Box\Nabeel Tahir Meetings\Meetings\Weekly Meetings\Meeting Jan 2026\Experiment 1_20_2026\Sample 1</t>
-  </si>
-  <si>
-    <t>C:\Users\mt1102\Box\Nabeel Tahir Meetings\Meetings\Weekly Meetings\Meeting Jan 2026\Experiment 1_23_2026\Sample 1</t>
-  </si>
-  <si>
-    <t>C:\Users\mt1102\Box\Nabeel Tahir Meetings\Meetings\Weekly Meetings\Meeting Jan 2026\Experiment 1_23_2026\Sample 2</t>
-  </si>
-  <si>
-    <t>C:\Users\mt1102\Box\Nabeel Tahir Meetings\Meetings\Weekly Meetings\Meeting Feb 2026\Experiment 2_5_2026\Sample 1</t>
-  </si>
-  <si>
-    <t>C:\Users\mt1102\Box\Nabeel Tahir Meetings\Meetings\Weekly Meetings\Meeting Feb 2026\Experiment 2_5_2026\Sample 2</t>
-  </si>
-  <si>
-    <t>C:\Users\mt1102\Box\Nabeel Tahir Meetings\Meetings\Weekly Meetings\Meeting March 2026\Experiment 3_18_2026\Sample 1</t>
-  </si>
-  <si>
-    <t>C:\Users\mt1102\Box\Nabeel Tahir Meetings\Meetings\Weekly Meetings\Meeting March 2026\Experiment 3_18_2026\Sample 2</t>
+    <t>C:\Users\mt1102\Box\Nabeel Tahir Meetings\Meetings\Weekly Meetings\Meeting Jan 2026\Experiment 1_14_2026\</t>
+  </si>
+  <si>
+    <t>C:\Users\mt1102\Box\Nabeel Tahir Meetings\Meetings\Weekly Meetings\Meeting Jan 2026\Experiment 1_20_2026\</t>
+  </si>
+  <si>
+    <t>C:\Users\mt1102\Box\Nabeel Tahir Meetings\Meetings\Weekly Meetings\Meeting Jan 2026\Experiment 1_23_2026\</t>
+  </si>
+  <si>
+    <t>C:\Users\mt1102\Box\Nabeel Tahir Meetings\Meetings\Weekly Meetings\Meeting Feb 2026\Experiment 2_5_2026\</t>
+  </si>
+  <si>
+    <t>C:\Users\mt1102\Box\Nabeel Tahir Meetings\Meetings\Weekly Meetings\Meeting March 2026\Experiment 3_18_2026\</t>
   </si>
 </sst>
 </file>
@@ -372,7 +360,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:A10"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
@@ -405,26 +393,6 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>9</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
